--- a/test/generator/baseline/gen.pptx.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.pptx.to.xlsx.xlsx
@@ -513,6 +513,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
 </worksheet>
 </file>
 
@@ -542,7 +545,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
@@ -1308,6 +1311,21 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+  </mergeCells>
 </worksheet>
 </file>
 

--- a/test/generator/baseline/gen.pptx.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.pptx.to.xlsx.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Tables 5" sheetId="5" r:id="rId5"/>
     <sheet name="Tables 6" sheetId="6" r:id="rId6"/>
     <sheet name="Text" sheetId="7" r:id="rId7"/>
+    <sheet name="Notes" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -391,8 +392,10 @@
       <c r="C3">
         <v>103</v>
       </c>
-      <c r="D3">
-        <v>7</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+7 </t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -445,8 +448,10 @@
       <c r="C6">
         <v>20</v>
       </c>
-      <c r="D6">
-        <v>4</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+4 </t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1764,4 +1769,70 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="74" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slide 1</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slide Note 1.
+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slide 2</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slide Note 2. This is a bold text, but no italic. Let's strike that out.
+2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slide 3</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">And then about tables
+3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slide 5</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Now calendars
+Sun
+Mon
+7. Sat
+5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/test/generator/baseline/gen.pptx.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.pptx.to.xlsx.xlsx
@@ -11,14 +11,18 @@
     <sheet name="Tables 4" sheetId="4" r:id="rId4"/>
     <sheet name="Tables 5" sheetId="5" r:id="rId5"/>
     <sheet name="Tables 6" sheetId="6" r:id="rId6"/>
-    <sheet name="Text" sheetId="7" r:id="rId7"/>
-    <sheet name="Notes" sheetId="8" r:id="rId8"/>
+    <sheet name="Charts Chart" sheetId="7" r:id="rId7"/>
+    <sheet name="Text" sheetId="8" r:id="rId8"/>
+    <sheet name="Notes" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -50,12 +54,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1337,6 +1342,102 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Series 1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Series 2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Series 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Category 1</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <v>4.3</v>
+      </c>
+      <c r="C2" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Category 2</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4000000000000004</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Category 3</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Category 4</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
     <col min="1" max="1" width="120" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1567,201 +1668,208 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no analogous technology in ebooks, so theconversion will usually end up placingthe image either centered or floating close to the point in the text where itwas inserted, notnecessarily where it appears on the page in Word.</t>
+          <t xml:space="preserve">165 Inspirational Quotes To Keep You Motivated In Life</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lists</t>
+          <t xml:space="preserve">There is no analogous technology in ebooks, so theconversion will usually end up placingthe image either centered or floating close to the point in the text where itwas inserted, notnecessarily where it appears on the page in Word.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">All types of lists are supported by the conversion, with the exception of lists that use fancy bullets, these get converted to regular bullets.</t>
+          <t xml:space="preserve">Lists</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulleted List</t>
+          <t xml:space="preserve">All types of lists are supported by the conversion, with the exception of lists that use fancy bullets, these get converted to regular bullets.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">Bulleted List</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">• One</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Numbered List</t>
+          <t xml:space="preserve">• Two</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">One, with a very long line to demonstrate that the hanging indent for the list is working correctly</t>
+          <t xml:space="preserve">Numbered List</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">1. One, with a very long line to demonstrate that the hanging indent for the list is working correctly</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-level Lists</t>
+          <t xml:space="preserve">2. Two</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">Multi-level Lists</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">1. One</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Three</t>
+          <t xml:space="preserve">1. Two</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four with a very long line to demonstrate that the hanging indent for the list is working correctly.</t>
+          <t xml:space="preserve">1. Three</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Five</t>
+          <t xml:space="preserve">2. Four with a very long line to demonstrate that the hanging indent for the list is working correctly.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Six</t>
+          <t xml:space="preserve">3. Five</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Multi-level list with bullets:</t>
+          <t xml:space="preserve">2. Six</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">A Multi-level list with bullets:</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">• One</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">This bullet uses an image as the bullet item</t>
+          <t xml:space="preserve">• Two</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four</t>
+          <t xml:space="preserve">• This bullet uses an image as the bullet item</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Five</t>
+          <t xml:space="preserve">• Four</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continued Lists</t>
+          <t xml:space="preserve">• Five</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">Continued Lists</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">1. One</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">An interruption in our regularly scheduled listing, for this essential and very relevant public service announcement.</t>
+          <t xml:space="preserve">2. Two</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">We now resume our normal programming</t>
+          <t xml:space="preserve">An interruption in our regularly scheduled listing, for this essential and very relevant public service announcement.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four</t>
+          <t xml:space="preserve">3. We now resume our normal programming</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Four</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Charts</t>
         </is>
@@ -1771,7 +1879,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>

--- a/test/generator/baseline/gen.pptx.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.pptx.to.xlsx.xlsx
@@ -1876,6 +1876,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A30" r:id="rId1"/>
+  </hyperlinks>
 </worksheet>
 </file>
 

--- a/test/generator/baseline/gen.pptx.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.pptx.to.xlsx.xlsx
@@ -567,7 +567,6 @@
     <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
     <col min="12" max="12" width="8" customWidth="1"/>
-    <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
   </cols>
   <sheetData>

--- a/test/generator/baseline/gen.pptx.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.pptx.to.xlsx.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tables 4" sheetId="4" r:id="rId4"/>
     <sheet name="Tables 5" sheetId="5" r:id="rId5"/>
     <sheet name="Tables 6" sheetId="6" r:id="rId6"/>
-    <sheet name="Charts Chart" sheetId="7" r:id="rId7"/>
+    <sheet name="Chart Title" sheetId="7" r:id="rId7"/>
     <sheet name="Text" sheetId="8" r:id="rId8"/>
     <sheet name="Notes" sheetId="9" r:id="rId9"/>
   </sheets>
@@ -1348,51 +1348,40 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chart Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
         <is>
           <t xml:space="preserve">Series 1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t xml:space="preserve">Series 2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Series 3</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Category 1</t>
-        </is>
-      </c>
-      <c r="B2" s="3">
-        <v>4.3</v>
-      </c>
-      <c r="C2" s="3">
-        <v>2.4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Category 2</t>
+          <t xml:space="preserve">Category 1</t>
         </is>
       </c>
       <c r="B3" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.4000000000000004</t>
-        </is>
+        <v>4.3</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2.4</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1401,36 +1390,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Category 3</t>
+          <t xml:space="preserve">Category 2</t>
         </is>
       </c>
       <c r="B4" s="3">
-        <v>3.5</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1.8</v>
+        <v>2.5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4000000000000004</t>
+        </is>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Category 3</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Category 4</t>
         </is>
       </c>
-      <c r="B5" s="3">
+      <c r="B6" s="3">
         <v>4.5</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C6" s="3">
         <v>2.8</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>5</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
 </worksheet>
 </file>
 
